--- a/artfynd/A 33589-2024 artfynd.xlsx
+++ b/artfynd/A 33589-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,6 +1006,965 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121589787</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>649754</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7170132</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121589781</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>649653</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7170246</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121589778</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>649707</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7170108</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121589782</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>649633</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7170230</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121589779</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>649708</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7170285</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121589785</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97059</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>649729</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7170230</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121589784</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>649702</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7170233</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121589780</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>649660</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7170277</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121589783</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>649652</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7170226</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33589-2024 artfynd.xlsx
+++ b/artfynd/A 33589-2024 artfynd.xlsx
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589787</v>
+        <v>121589780</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649754</v>
+        <v>649660</v>
       </c>
       <c r="R5" t="n">
-        <v>7170132</v>
+        <v>7170277</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589781</v>
+        <v>121589779</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649653</v>
+        <v>649708</v>
       </c>
       <c r="R6" t="n">
-        <v>7170246</v>
+        <v>7170285</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,6 +1194,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589778</v>
+        <v>121589787</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1264,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649707</v>
+        <v>649754</v>
       </c>
       <c r="R7" t="n">
-        <v>7170108</v>
+        <v>7170132</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589782</v>
+        <v>121589778</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1370,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649633</v>
+        <v>649707</v>
       </c>
       <c r="R8" t="n">
-        <v>7170230</v>
+        <v>7170108</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589779</v>
+        <v>121589782</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1476,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649708</v>
+        <v>649633</v>
       </c>
       <c r="R9" t="n">
-        <v>7170285</v>
+        <v>7170230</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1512,11 +1517,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589785</v>
+        <v>121589781</v>
       </c>
       <c r="B10" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,25 +1555,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649729</v>
+        <v>649653</v>
       </c>
       <c r="R10" t="n">
-        <v>7170230</v>
+        <v>7170246</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589780</v>
+        <v>121589785</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,25 +1767,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649660</v>
+        <v>649729</v>
       </c>
       <c r="R12" t="n">
-        <v>7170277</v>
+        <v>7170230</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 33589-2024 artfynd.xlsx
+++ b/artfynd/A 33589-2024 artfynd.xlsx
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589780</v>
+        <v>121589784</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649660</v>
+        <v>649702</v>
       </c>
       <c r="R5" t="n">
-        <v>7170277</v>
+        <v>7170233</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589779</v>
+        <v>121589782</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649708</v>
+        <v>649633</v>
       </c>
       <c r="R6" t="n">
-        <v>7170285</v>
+        <v>7170230</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,11 +1194,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589787</v>
+        <v>121589781</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1269,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649754</v>
+        <v>649653</v>
       </c>
       <c r="R7" t="n">
-        <v>7170132</v>
+        <v>7170246</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1437,7 +1432,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589782</v>
+        <v>121589780</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1481,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649633</v>
+        <v>649660</v>
       </c>
       <c r="R9" t="n">
-        <v>7170230</v>
+        <v>7170277</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1543,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589781</v>
+        <v>121589785</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,25 +1550,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1587,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649653</v>
+        <v>649729</v>
       </c>
       <c r="R10" t="n">
-        <v>7170246</v>
+        <v>7170230</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1649,7 +1644,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589784</v>
+        <v>121589787</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1693,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649702</v>
+        <v>649754</v>
       </c>
       <c r="R11" t="n">
-        <v>7170233</v>
+        <v>7170132</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1755,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589785</v>
+        <v>121589779</v>
       </c>
       <c r="B12" t="n">
-        <v>97059</v>
+        <v>57372</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,25 +1762,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1799,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649729</v>
+        <v>649708</v>
       </c>
       <c r="R12" t="n">
-        <v>7170230</v>
+        <v>7170285</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1835,6 +1830,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 33589-2024 artfynd.xlsx
+++ b/artfynd/A 33589-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589784</v>
+        <v>121589780</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649702</v>
+        <v>649660</v>
       </c>
       <c r="R5" t="n">
-        <v>7170233</v>
+        <v>7170277</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589782</v>
+        <v>121589779</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649633</v>
+        <v>649708</v>
       </c>
       <c r="R6" t="n">
-        <v>7170230</v>
+        <v>7170285</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,6 +1194,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589781</v>
+        <v>121589778</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649653</v>
+        <v>649707</v>
       </c>
       <c r="R7" t="n">
-        <v>7170246</v>
+        <v>7170108</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589778</v>
+        <v>121589782</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649707</v>
+        <v>649633</v>
       </c>
       <c r="R8" t="n">
-        <v>7170108</v>
+        <v>7170230</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589780</v>
+        <v>121589787</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649660</v>
+        <v>649754</v>
       </c>
       <c r="R9" t="n">
-        <v>7170277</v>
+        <v>7170132</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589785</v>
+        <v>121589784</v>
       </c>
       <c r="B10" t="n">
-        <v>97059</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,25 +1555,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1582,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649729</v>
+        <v>649702</v>
       </c>
       <c r="R10" t="n">
-        <v>7170230</v>
+        <v>7170233</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589787</v>
+        <v>121589785</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>97067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,25 +1661,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1688,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649754</v>
+        <v>649729</v>
       </c>
       <c r="R11" t="n">
-        <v>7170132</v>
+        <v>7170230</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1750,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589779</v>
+        <v>121589781</v>
       </c>
       <c r="B12" t="n">
-        <v>57372</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1794,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649708</v>
+        <v>649653</v>
       </c>
       <c r="R12" t="n">
-        <v>7170285</v>
+        <v>7170246</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1830,11 +1835,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,7 +1864,7 @@
         <v>121589783</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 33589-2024 artfynd.xlsx
+++ b/artfynd/A 33589-2024 artfynd.xlsx
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589778</v>
+        <v>121589780</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649707</v>
+        <v>649660</v>
       </c>
       <c r="R5" t="n">
-        <v>7170108</v>
+        <v>7170277</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589779</v>
+        <v>121589778</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649708</v>
+        <v>649707</v>
       </c>
       <c r="R6" t="n">
-        <v>7170285</v>
+        <v>7170108</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,11 +1194,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589783</v>
+        <v>121589782</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1269,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649652</v>
+        <v>649633</v>
       </c>
       <c r="R7" t="n">
-        <v>7170226</v>
+        <v>7170230</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1331,7 +1326,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589780</v>
+        <v>121589787</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1375,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649660</v>
+        <v>649754</v>
       </c>
       <c r="R8" t="n">
-        <v>7170277</v>
+        <v>7170132</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1543,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589784</v>
+        <v>121589779</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,21 +1554,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1587,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649702</v>
+        <v>649708</v>
       </c>
       <c r="R10" t="n">
-        <v>7170233</v>
+        <v>7170285</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1623,6 +1618,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589787</v>
+        <v>121589781</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649754</v>
+        <v>649653</v>
       </c>
       <c r="R11" t="n">
-        <v>7170132</v>
+        <v>7170246</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589782</v>
+        <v>121589783</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649633</v>
+        <v>649652</v>
       </c>
       <c r="R12" t="n">
-        <v>7170230</v>
+        <v>7170226</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,7 +1861,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589781</v>
+        <v>121589784</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>649653</v>
+        <v>649702</v>
       </c>
       <c r="R13" t="n">
-        <v>7170246</v>
+        <v>7170233</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 33589-2024 artfynd.xlsx
+++ b/artfynd/A 33589-2024 artfynd.xlsx
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589780</v>
+        <v>121589782</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649660</v>
+        <v>649633</v>
       </c>
       <c r="R5" t="n">
-        <v>7170277</v>
+        <v>7170230</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589778</v>
+        <v>121589780</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649707</v>
+        <v>649660</v>
       </c>
       <c r="R6" t="n">
-        <v>7170108</v>
+        <v>7170277</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589782</v>
+        <v>121589781</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649633</v>
+        <v>649653</v>
       </c>
       <c r="R7" t="n">
-        <v>7170230</v>
+        <v>7170246</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589787</v>
+        <v>121589785</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,25 +1338,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649754</v>
+        <v>649729</v>
       </c>
       <c r="R8" t="n">
-        <v>7170132</v>
+        <v>7170230</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589785</v>
+        <v>121589783</v>
       </c>
       <c r="B9" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,25 +1444,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649729</v>
+        <v>649652</v>
       </c>
       <c r="R9" t="n">
-        <v>7170230</v>
+        <v>7170226</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589781</v>
+        <v>121589784</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649653</v>
+        <v>649702</v>
       </c>
       <c r="R11" t="n">
-        <v>7170246</v>
+        <v>7170233</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589783</v>
+        <v>121589787</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649652</v>
+        <v>649754</v>
       </c>
       <c r="R12" t="n">
-        <v>7170226</v>
+        <v>7170132</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,7 +1861,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589784</v>
+        <v>121589778</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>649702</v>
+        <v>649707</v>
       </c>
       <c r="R13" t="n">
-        <v>7170233</v>
+        <v>7170108</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 33589-2024 artfynd.xlsx
+++ b/artfynd/A 33589-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113888247</v>
+        <v>113886472</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>649725</v>
+        <v>649668</v>
       </c>
       <c r="R2" t="n">
-        <v>7170254</v>
+        <v>7170240</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113886565</v>
+        <v>121589778</v>
       </c>
       <c r="B3" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -826,14 +816,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tallträsk, Ly lm</t>
+          <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>649784</v>
+        <v>649707</v>
       </c>
       <c r="R3" t="n">
-        <v>7170146</v>
+        <v>7170108</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,17 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,49 +870,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113886472</v>
+        <v>121589780</v>
       </c>
       <c r="B4" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,14 +917,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tallträsk, Ly lm</t>
+          <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>649668</v>
+        <v>649660</v>
       </c>
       <c r="R4" t="n">
-        <v>7170240</v>
+        <v>7170277</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,17 +951,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,12 +971,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1011,16 +986,11 @@
         <v>121589781</v>
       </c>
       <c r="B5" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1114,19 +1084,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589780</v>
+        <v>121589782</v>
       </c>
       <c r="B6" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1158,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649660</v>
+        <v>649633</v>
       </c>
       <c r="R6" t="n">
-        <v>7170277</v>
+        <v>7170230</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,19 +1185,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589787</v>
+        <v>121589783</v>
       </c>
       <c r="B7" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1264,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649754</v>
+        <v>649652</v>
       </c>
       <c r="R7" t="n">
-        <v>7170132</v>
+        <v>7170226</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,19 +1286,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589782</v>
+        <v>121589784</v>
       </c>
       <c r="B8" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1370,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649633</v>
+        <v>649702</v>
       </c>
       <c r="R8" t="n">
-        <v>7170230</v>
+        <v>7170233</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,19 +1387,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589783</v>
+        <v>121589787</v>
       </c>
       <c r="B9" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1476,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649652</v>
+        <v>649754</v>
       </c>
       <c r="R9" t="n">
-        <v>7170226</v>
+        <v>7170132</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,15 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589785</v>
+        <v>121589779</v>
       </c>
       <c r="B10" t="n">
-        <v>97085</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,21 +1499,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1582,10 +1527,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649729</v>
+        <v>649708</v>
       </c>
       <c r="R10" t="n">
-        <v>7170230</v>
+        <v>7170285</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1618,6 +1563,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,19 +1594,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589779</v>
+        <v>121589789</v>
       </c>
       <c r="B11" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1688,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649708</v>
+        <v>649849</v>
       </c>
       <c r="R11" t="n">
-        <v>7170285</v>
+        <v>7170087</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1728,7 +1673,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Födosökshack på tallhögstubbe</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,15 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589784</v>
+        <v>113888247</v>
       </c>
       <c r="B12" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1795,14 +1735,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fäboliden, Ly lm</t>
+          <t>Tallträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649702</v>
+        <v>649725</v>
       </c>
       <c r="R12" t="n">
-        <v>7170233</v>
+        <v>7170254</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1829,12 +1769,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,49 +1794,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589778</v>
+        <v>121589785</v>
       </c>
       <c r="B13" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1905,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>649707</v>
+        <v>649729</v>
       </c>
       <c r="R13" t="n">
-        <v>7170108</v>
+        <v>7170230</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1964,6 +1904,208 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121589786</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>649766</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7170201</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121589790</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>649837</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7170108</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33589-2024 artfynd.xlsx
+++ b/artfynd/A 33589-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589778</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589787</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589789</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589790</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886472</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589780</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589781</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589782</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1591,6 +1636,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589783</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589784</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589779</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888247</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2005,6 +2070,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589785</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2106,8 +2176,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589786</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>